--- a/artfynd/A 35901-2024 artfynd.xlsx
+++ b/artfynd/A 35901-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121245029</v>
       </c>
       <c r="B2" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 35901-2024 artfynd.xlsx
+++ b/artfynd/A 35901-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121245029</v>
       </c>
       <c r="B2" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 35901-2024 artfynd.xlsx
+++ b/artfynd/A 35901-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121245029</v>
       </c>
       <c r="B2" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 35901-2024 artfynd.xlsx
+++ b/artfynd/A 35901-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121245029</v>
       </c>
       <c r="B2" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
